--- a/HSI_FSC_result/2. Dropout/result_dropout_parameters.xlsx
+++ b/HSI_FSC_result/2. Dropout/result_dropout_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\2. Dropout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7225D671-DEDF-40C6-94AF-41A02980C59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BFEA37-CC31-4451-8435-A27AB47CD8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
